--- a/data/trans_dic/P22$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 0,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,1</t>
+          <t>0,0; 0,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,82</t>
+          <t>0,18; 1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,86</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,96</t>
+          <t>0,11; 0,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
     </row>
@@ -997,52 +997,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,32 +1157,32 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,64</t>
+          <t>0,06; 0,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,43</t>
+          <t>0,04; 0,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,51</t>
+          <t>0,05; 0,5</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1557,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,29</t>
+          <t>0,04; 0,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,45</t>
+          <t>0,07; 0,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,25</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,18</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>0,02; 0,25</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,22</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,19</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,25</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,34</t>
+          <t>0,07; 0,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,26</t>
+          <t>0,05; 0,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,18</t>
+          <t>0,02; 0,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,07; 0,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,23</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene Seguro Sanitario</t>
+          <t>Población que no tiene seguro médico (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5679</t>
+          <t>0; 6971</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 972</t>
+          <t>0; 850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5291</t>
+          <t>0; 5321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7756</t>
+          <t>0; 4988</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6832</t>
+          <t>0; 5576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 730</t>
+          <t>0; 827</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5547</t>
+          <t>0; 4647</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8704</t>
+          <t>0; 8163</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1056; 10733</t>
+          <t>1055; 11142</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7534</t>
+          <t>0; 7133</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4905</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6317</t>
+          <t>0; 5803</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5600</t>
+          <t>0; 6175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1197; 11096</t>
+          <t>1191; 10945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1223; 11021</t>
+          <t>1227; 11283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 7247</t>
+          <t>0; 6179</t>
         </is>
       </c>
     </row>
@@ -2484,57 +2484,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11430</t>
+          <t>0; 14718</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2008</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6106</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2010</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 3180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 11519</t>
+          <t>0; 10367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6119</t>
+          <t>0; 6089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8835</t>
+          <t>0; 9158</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2149</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7752</t>
+          <t>0; 11082</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5517</t>
+          <t>0; 5548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2191</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>375; 4570</t>
+          <t>396; 5125</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 10123</t>
+          <t>0; 9826</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2172</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8860</t>
+          <t>0; 8863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>680; 6866</t>
+          <t>642; 7558</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2159</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3385</t>
+          <t>0; 4716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3708</t>
+          <t>0; 4311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1925</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2106</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2182</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>607; 5685</t>
+          <t>607; 5566</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1847</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2101</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6113</t>
+          <t>0; 5410</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1411</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5010</t>
+          <t>0; 4433</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6216</t>
+          <t>0; 5433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4937</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1823</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6250</t>
+          <t>0; 6162</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 3895</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2141</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 6962</t>
+          <t>0; 5548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>0; 3900</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1652; 14932</t>
+          <t>1659; 15454</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1210; 9909</t>
+          <t>1211; 11066</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2268; 15345</t>
+          <t>2281; 14424</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>766; 8713</t>
+          <t>893; 8496</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 6591</t>
+          <t>0; 6466</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>849; 8843</t>
+          <t>850; 8879</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2888; 12462</t>
+          <t>2627; 11475</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3377; 17536</t>
+          <t>3139; 16800</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1234; 12286</t>
+          <t>1230; 12221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4332; 18989</t>
+          <t>5010; 19820</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4762; 16226</t>
+          <t>4660; 15786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$notiene-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,21</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,12</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,89</t>
+          <t>0,18; 1,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,98</t>
+          <t>0,11; 1,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,72</t>
+          <t>0,06; 0,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,47</t>
+          <t>0,05; 0,56</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,5</t>
+          <t>0,06; 0,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,74</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,73</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,7</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,76</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,51</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,27 +1664,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,32</t>
+          <t>0,04; 0,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,07; 0,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,25</t>
+          <t>0,03; 0,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,21</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,19</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,18</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,25</t>
+          <t>0,02; 0,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,31</t>
+          <t>0,09; 0,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,25</t>
+          <t>0,04; 0,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,17</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,29</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,09; 0,29</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6971</t>
+          <t>0; 4977</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 850</t>
+          <t>0; 9148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5321</t>
+          <t>0; 5314</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4988</t>
+          <t>0; 6322</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5576</t>
+          <t>0; 6928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 827</t>
+          <t>0; 9445</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1335</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8163</t>
+          <t>0; 8657</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1055; 11142</t>
+          <t>1050; 10289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2301,37 +2301,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7133</t>
+          <t>0; 5990</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 4690</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5803</t>
+          <t>0; 6690</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6175</t>
+          <t>0; 5450</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1191; 10945</t>
+          <t>1199; 9952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1227; 11283</t>
+          <t>1225; 12000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6179</t>
+          <t>0; 7524</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>781</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>781</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 14718</t>
+          <t>0; 9985</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5079</t>
+          <t>0; 6090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>0; 4692</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 10367</t>
+          <t>0; 12878</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6089</t>
+          <t>0; 6689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3501</t>
+          <t>0; 3908</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3052</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9158</t>
+          <t>0; 10432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 11082</t>
+          <t>0; 8790</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5548</t>
+          <t>0; 5765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>396; 5125</t>
+          <t>442; 5635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 9826</t>
+          <t>0; 8855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8863</t>
+          <t>0; 11451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>642; 7558</t>
+          <t>759; 8049</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2322</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4716</t>
+          <t>0; 4471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>607; 5566</t>
+          <t>706; 6369</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3814</t>
+          <t>0; 5236</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5410</t>
+          <t>0; 5854</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 4688</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5433</t>
+          <t>0; 5191</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>0; 5924</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1211</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6162</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3895</t>
+          <t>0; 4246</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5548</t>
+          <t>0; 6917</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>0; 3713</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>11577</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1659; 15454</t>
+          <t>1656; 15998</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1211; 11066</t>
+          <t>1211; 9987</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2281; 14424</t>
+          <t>2448; 15129</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>893; 8496</t>
+          <t>1142; 12727</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6450</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 6466</t>
+          <t>0; 6855</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>850; 8879</t>
+          <t>849; 9559</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2627; 11475</t>
+          <t>3324; 13001</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3139; 16800</t>
+          <t>2864; 17250</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1230; 12221</t>
+          <t>1266; 12256</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5010; 19820</t>
+          <t>4345; 17970</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4660; 15786</t>
+          <t>6248; 20926</t>
         </is>
       </c>
     </row>
